--- a/app/static/Vocaburn_Template.xlsx
+++ b/app/static/Vocaburn_Template.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -27,15 +27,63 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="001E1B4B"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Consolas"/>
+      <b val="1"/>
+      <color rgb="003730A3"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="00111827"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="004B5563"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Consolas"/>
+      <color rgb="00059669"/>
+      <sz val="9"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="004F46E5"/>
+        <bgColor rgb="004F46E5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EEF2FF"/>
+        <bgColor rgb="00EEF2FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00059669"/>
+        <bgColor rgb="00059669"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -47,19 +95,45 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color rgb="00E5E7EB"/>
+      </left>
+      <right style="thin">
+        <color rgb="00E5E7EB"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E5E7EB"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E5E7EB"/>
+      </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -426,10 +500,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:E34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="36" customWidth="1" min="4" max="4"/>
+    <col width="65" customWidth="1" min="5" max="5"/>
+  </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Key</t>
@@ -440,68 +521,802 @@
           <t>Value</t>
         </is>
       </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Title</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>My Neural Quiz</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Description</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>This is a sample quiz imported from Excel.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Tags</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>JLPT, N1, Grammar</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Time_Limit</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>60</t>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Tên Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Tùy Chọn Hợp Lệ</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Hướng Dẫn &amp; Giải Thích Chi Tiết</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>--- THÔNG TIN CHUNG BỘ THẺ (General Information) ---</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>500 Từ Vựng N2 Cơ Bản</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>Tên bộ thẻ</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>Văn bản tự do</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>BẮT BUỘC: Tiêu đề hiển thị của bộ thẻ flashcard</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>Bộ thẻ luyện từ vựng N2 tiếng Nhật có audio và ví dụ minh họa</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>Mô tả bộ thẻ</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>Văn bản tự do</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>Mô tả tóm tắt nội dung, đối tượng học và mục tiêu</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>category</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Tiếng Nhật</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>Danh mục</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>General, Tiếng Nhật, Tiếng Anh, Y Khoa...</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>Tên danh mục phân loại bộ thẻ (hệ thống tự tạo nếu chưa có)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>tags</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>JLPT, N2, Từ vựng, Kanji</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>Thẻ phân loại</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>Các từ khóa cách nhau bằng dấu phẩy (,)</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>Thẻ tìm kiếm giúp người dùng dễ dàng lọc và khám phá</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="20" customHeight="1">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>cover_image</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>https://images.unsplash.com/photo-1528164344705-475426879c0d</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>URL Ảnh bìa</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>URL ảnh hợp lệ (jpg, png, webp)</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>Ảnh minh họa bìa hiển thị trên danh sách bộ thẻ</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>instruction</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>Hãy đọc to từ vựng trước khi lật mặt sau kiểm tra nghĩa.</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>Hướng dẫn học</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>Văn bản tự do</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>Ghi chú, mẹo hoặc chỉ dẫn của giáo viên dành cho học viên</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>is_public</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>Công khai</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>TRUE | FALSE</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>TRUE: Mọi người đều có thể tìm và học. FALSE: Chỉ riêng bạn xem được</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>time_limit</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>Giới hạn thời gian</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>Số nguyên (phút), 0 = Không giới hạn</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>Thời gian làm bài tối đa khi người học luyện tập bộ thẻ này</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>--- CÀI ĐẶT HỌC MẶC ĐỊNH ĐẦU VÀO (Creator Study Defaults) ---</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>study_autoplay_audio</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>front</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>Tự động phát âm thanh</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>none | front | back | always</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>Tự động phát TTS/Audio: none (tắt), front (mặt trước), back (mặt sau), always (cả hai)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>study_show_images</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>always</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>Hiển thị hình ảnh</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>always | front | back | none</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>Chế độ ảnh: always (luôn hiện), front (chỉ mặt trước), back (chỉ mặt sau), none (ẩn ảnh)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>study_learning_mode</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>fsrs</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>Chế độ học mặc định</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>fsrs | roadmap | new | review | hardest | flip</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>Chế độ khởi đầu khi người học bấm học thẻ: fsrs (giãn cách), roadmap (lộ trình), flip (lật nhanh)...</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>study_random_enabled</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>Xáo trộn thứ tự thẻ</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>TRUE | FALSE</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>TRUE: Ngẫu nhiên thứ tự thẻ khi bắt đầu học; FALSE: Theo thứ tự gốc trong bảng</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>study_sfx_enabled</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>Âm thanh hiệu ứng</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>TRUE | FALSE</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>TRUE: Bật âm thanh chúc mừng / âm thanh phản hồi thao tác</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="20" customHeight="1">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>study_quick_learn_enabled</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>Chế độ học nhanh</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>TRUE | FALSE</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>TRUE: Tự động chuyển thẻ kế tiếp ngay khi người học chọn hoặc đánh giá</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="20" customHeight="1">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>study_haptic_enabled</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>Rung phản hồi (Điện thoại)</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>TRUE | FALSE</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>TRUE: Rung nhẹ thiết bị khi thao tác trên ứng dụng di động</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="20" customHeight="1">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>study_show_fsrs</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>Nút đánh giá FSRS</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>TRUE | FALSE</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>TRUE: Hiển thị 4 nút đánh giá FSRS (Again, Hard, Good, Easy)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="22" customHeight="1">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>--- CẤU HÌNH LUYỆN TẬP ĐA CHẾ ĐỘ (Practice Modes &amp; Pairs) ---</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="20" customHeight="1">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>mcq_active_pairs</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>front-back, back-front</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>Cặp luyện tập trắc nghiệm</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>Cặp tên cột dạng: q-a, q2-a2</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>Cột câu hỏi và cột đáp án tạo đề trắc nghiệm 4 đáp án</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="20" customHeight="1">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>mcq_num_choices</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>Số lựa chọn trắc nghiệm</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>Từ 3 đến 8 (mặc định 4)</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>Số lượng đáp án A, B, C, D... hiển thị cho mỗi câu hỏi</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="20" customHeight="1">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>typing_active_pairs</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>back-front</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>Cặp luyện tập gõ từ</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>Cặp tên cột dạng: q-a</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>Hiển thị cột q (gợi ý nghĩa) và yêu cầu người học gõ chính xác cột a</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="20" customHeight="1">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>listening_active_pairs</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>front_audio-back</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>Cặp luyện tập nghe hiểu</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>Cặp tên cột dạng: q-a</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>Chế độ nghe audio phát ra và bấm chọn đáp án đúng</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="20" customHeight="1">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>listening_num_choices</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>Số lựa chọn bài nghe</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>Từ 3 đến 8 (mặc định 4)</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>Số lựa chọn đáp án hiển thị trong bài luyện tập nghe</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="22" customHeight="1">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>--- CẤU HÌNH TRÍ TUỆ NHÂN TẠO AI (AI Prompts) ---</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="20" customHeight="1">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>ai_prompt_explanation</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>Hãy giải thích chi tiết ý nghĩa và ngữ cảnh sử dụng của từ này.</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>Prompt giải thích từ vựng</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>Câu lệnh AI tự do</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>Lời nhắc gửi tới AI khi người học bấm nút 'Giải thích bằng AI'</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="20" customHeight="1">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>ai_prompt_hint</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>Hãy tạo 1 câu đố ngắn không chứa từ khóa để người học tự đoán.</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>Prompt gợi ý (Hint)</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="inlineStr">
+        <is>
+          <t>Câu lệnh AI tự do</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>Lời nhắc gửi tới AI để sinh gợi ý khi người học gặp khó</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="20" customHeight="1">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>ai_prompt_mnemonic</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>Hãy tạo mẹo ghi nhớ vui nhộn hoặc chiết tự chữ Hán cho từ này.</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>Prompt mẹo ghi nhớ</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="inlineStr">
+        <is>
+          <t>Câu lệnh AI tự do</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>Lời nhắc gửi tới AI để tạo câu chuyện ghi nhớ từ vựng</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="22" customHeight="1">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>--- QUẢN LÝ CỘNG TÁC VIÊN (Collaborators) ---</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="20" customHeight="1">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>collaborators</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>teacher_minh:editor, trogiang_nam:editor</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>Cộng tác viên biên tập</t>
+        </is>
+      </c>
+      <c r="D31" s="6" t="inlineStr">
+        <is>
+          <t>username:role (editor | viewer)</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>Danh sách người dùng được quyền xem hoặc cùng sửa bộ thẻ, cách nhau dấu phẩy</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="22" customHeight="1">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>--- CẤU HÌNH NÂNG CAO (Advanced JSON Backup) ---</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="20" customHeight="1">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>study_defaults</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>JSON cấu hình học mặc định</t>
+        </is>
+      </c>
+      <c r="D33" s="6" t="inlineStr">
+        <is>
+          <t>Chuỗi JSON hợp lệ</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t>Chuỗi JSON chứa tất cả study_defaults (tự động cập nhật nếu nhập lẻ bên trên)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="20" customHeight="1">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>practice_settings</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>JSON toàn bộ practice settings</t>
+        </is>
+      </c>
+      <c r="D34" s="6" t="inlineStr">
+        <is>
+          <t>Chuỗi JSON hợp lệ</t>
+        </is>
+      </c>
+      <c r="E34" s="5" t="inlineStr">
+        <is>
+          <t>Chuỗi JSON sao lưu toàn diện tất cả các tab cấu hình bộ thẻ</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A30:E30"/>
+    <mergeCell ref="A26:E26"/>
+    <mergeCell ref="A20:E20"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A11:E11"/>
+    <mergeCell ref="A32:E32"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -512,132 +1327,224 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:L4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="20" customWidth="1" min="12" max="12"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Question</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Option_A</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Option_B</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Option_C</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Option_D</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Answer</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Explanation</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>AI Analysis</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Hệ mặt trời có bao nhiêu hành tinh?</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Sao Diêm Vương không còn được coi là hành tinh từ năm 2006.</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Phân tích chuyên sâu về hệ mặt trời...</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Ai là người phát triển thuyết tương đối?</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Isaac Newton</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Albert Einstein</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Nikola Tesla</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Galileo Galilei</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Albert Einstein công bố thuyết tương đối hẹp vào năm 1905.</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Phân tích về vật lý hiện đại...</t>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>front</t>
+        </is>
+      </c>
+      <c r="B1" s="7" t="inlineStr">
+        <is>
+          <t>back</t>
+        </is>
+      </c>
+      <c r="C1" s="7" t="inlineStr">
+        <is>
+          <t>explanation</t>
+        </is>
+      </c>
+      <c r="D1" s="7" t="inlineStr">
+        <is>
+          <t>front_audio_content</t>
+        </is>
+      </c>
+      <c r="E1" s="7" t="inlineStr">
+        <is>
+          <t>back_audio_content</t>
+        </is>
+      </c>
+      <c r="F1" s="7" t="inlineStr">
+        <is>
+          <t>front_audio_url</t>
+        </is>
+      </c>
+      <c r="G1" s="7" t="inlineStr">
+        <is>
+          <t>back_audio_url</t>
+        </is>
+      </c>
+      <c r="H1" s="7" t="inlineStr">
+        <is>
+          <t>front_img</t>
+        </is>
+      </c>
+      <c r="I1" s="7" t="inlineStr">
+        <is>
+          <t>back_img</t>
+        </is>
+      </c>
+      <c r="J1" s="7" t="inlineStr">
+        <is>
+          <t>kanji</t>
+        </is>
+      </c>
+      <c r="K1" s="7" t="inlineStr">
+        <is>
+          <t>furigana</t>
+        </is>
+      </c>
+      <c r="L1" s="7" t="inlineStr">
+        <is>
+          <t>example</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>こんにちは</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>Xin chào</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>Lời chào thông dụng buổi sáng/chiều trong giao tiếp tiếng Nhật.</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>こんにちは</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>Xin chào</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr"/>
+      <c r="G2" s="4" t="inlineStr"/>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>https://images.unsplash.com/photo-1528164344705-475426879c0d</t>
+        </is>
+      </c>
+      <c r="I2" s="4" t="inlineStr"/>
+      <c r="J2" s="4" t="inlineStr">
+        <is>
+          <t>今日</t>
+        </is>
+      </c>
+      <c r="K2" s="4" t="inlineStr">
+        <is>
+          <t>konnichiwa</t>
+        </is>
+      </c>
+      <c r="L2" s="4" t="inlineStr">
+        <is>
+          <t>皆さん、こんにちは！</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>ありがとう</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>Cảm ơn</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>Lời cảm ơn lịch sự cơ bản.</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>ありがとう</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>Cảm ơn</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr"/>
+      <c r="G3" s="4" t="inlineStr"/>
+      <c r="H3" s="4" t="inlineStr"/>
+      <c r="I3" s="4" t="inlineStr"/>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>有難う</t>
+        </is>
+      </c>
+      <c r="K3" s="4" t="inlineStr">
+        <is>
+          <t>arigatou</t>
+        </is>
+      </c>
+      <c r="L3" s="4" t="inlineStr">
+        <is>
+          <t>どうもありがとうございます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>勉強 (べんきょう)</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>Học tập, học hỏi</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>Danh từ hoặc động từ Suru: học tập chuyên cần.</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>べんきょう</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>Học tập</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr"/>
+      <c r="G4" s="4" t="inlineStr"/>
+      <c r="H4" s="4" t="inlineStr"/>
+      <c r="I4" s="4" t="inlineStr"/>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>勉強</t>
+        </is>
+      </c>
+      <c r="K4" s="4" t="inlineStr">
+        <is>
+          <t>benkyou</t>
+        </is>
+      </c>
+      <c r="L4" s="4" t="inlineStr">
+        <is>
+          <t>毎日日本語を勉強しています。</t>
         </is>
       </c>
     </row>
